--- a/planejamento.xlsx
+++ b/planejamento.xlsx
@@ -223,15 +223,15 @@
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 160/2025
-CHEGADA: 24/03</t>
+CHEGADA: 10/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 146/2025
-CHEGADA: 25/03</t>
+CHEGADA: 05/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 167/2025
-CHEGADA: 26/03</t>
+CHEGADA: 03/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 157/2025
@@ -243,7 +243,7 @@
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 173/2025
-SAÍDA: 29/03</t>
+SAÍDA: 05/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 164/2025
@@ -251,21 +251,21 @@
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: XXX/2025
-SAÍDA: 31/03</t>
+SAÍDA: 01/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: XXX/2025
-SAÍDA: 01/04</t>
+SAÍDA: 24/03</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 
 XXX/2026
-SAÍDA: 02/04</t>
+SAÍDA: 25/03</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 
 XXX/2026
-SAÍDA: 03/04</t>
+SAÍDA: 01/04</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO: 
@@ -1813,11 +1813,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="90737224"/>
-        <c:axId val="34539215"/>
+        <c:axId val="18044403"/>
+        <c:axId val="7704325"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90737224"/>
+        <c:axId val="18044403"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1849,14 +1849,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34539215"/>
+        <c:crossAx val="7704325"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="34539215"/>
+        <c:axId val="7704325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1897,7 +1897,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90737224"/>
+        <c:crossAx val="18044403"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1935,9 +1935,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>1139760</xdr:colOff>
+      <xdr:colOff>1139400</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>183960</xdr:rowOff>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1946,7 +1946,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6649200" y="2359080"/>
-        <a:ext cx="12080160" cy="4444920"/>
+        <a:ext cx="12079800" cy="4444560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">

--- a/planejamento.xlsx
+++ b/planejamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3478" documentId="13_ncr:1_{4436CD64-1579-4EFD-B7A1-670FDD183420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E3A413-7443-4A84-9E0C-922B59AA0958}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B8E605-53F7-40C5-AD40-FF7928846F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,20 +259,8 @@
 CHEGADA: 05/04</t>
   </si>
   <si>
-    <t>CONTRATO: 150/2025
-CHEGADA: 25/03</t>
-  </si>
-  <si>
     <t>CONTRATO: 160/2025
 CHEGADA: 25/03</t>
-  </si>
-  <si>
-    <t>CONTRATO: 146/2025
-CHEGADA: 27/03</t>
-  </si>
-  <si>
-    <t>CONTRATO: 167/2025
-CHEGADA: 30/03</t>
   </si>
   <si>
     <t>CONTRATO: 157/2025
@@ -281,14 +269,6 @@
   <si>
     <t>CONTRATO: 126/2025
 CHEGADA: 15/04</t>
-  </si>
-  <si>
-    <t>CONTRATO: 135/2025
-SAÍDA: 20/03</t>
-  </si>
-  <si>
-    <t>CONTRATO: 172/2025
-SAÍDA: 20/03</t>
   </si>
   <si>
     <t>CONTRATO: 171/2025
@@ -1088,6 +1068,26 @@
   <si>
     <t>Peso</t>
   </si>
+  <si>
+    <t>CONTRATO: 135/2025
+SAÍDA: 28/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 172/2025
+SAÍDA: 02/04</t>
+  </si>
+  <si>
+    <t>CONTRATO: 146/2025
+CHEGADA: 28/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 167/2025
+CHEGADA: 31/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 150/2025
+CHEGADA: 04/04</t>
+  </si>
 </sst>
 </file>
 
@@ -1097,7 +1097,7 @@
     <numFmt numFmtId="164" formatCode="d/mmm"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1685,54 +1685,6 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1753,6 +1705,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1775,8 +1730,53 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2399,7 +2399,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -2417,9 +2417,9 @@
     <col min="19" max="21" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="37.9" customHeight="1">
-      <c r="A1" s="47"/>
-      <c r="B1" s="48" t="s">
+    <row r="1" spans="1:21" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="76"/>
+      <c r="B1" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2472,91 +2472,91 @@
       <c r="T1" s="5"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="49" t="s">
+    <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="49" t="s">
+      <c r="J2" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="49" t="s">
+      <c r="K2" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="L2" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="50" t="s">
+      <c r="P2" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="50" t="s">
+      <c r="R2" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="50" t="s">
+      <c r="S2" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="50" t="s">
+      <c r="T2" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="50" t="s">
+      <c r="U2" s="74" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="28.5" customHeight="1">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
+    <row r="3" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="74"/>
     </row>
-    <row r="4" spans="1:21" ht="52.9" customHeight="1">
+    <row r="4" spans="1:21" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>31</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27.6" customHeight="1">
+    <row r="5" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>32</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>11968</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15" customHeight="1">
+    <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>46015</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>88658.95</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15" customHeight="1">
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>46020</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>79117.399999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15" customHeight="1">
+    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>46027</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>120491.95949999998</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="15" customHeight="1">
+    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>46029</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>106667.89649999999</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="15" customHeight="1">
+    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>46030</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>92086.318499999979</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" customHeight="1">
+    <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>46034</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>99459.970499999996</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="15" customHeight="1">
+    <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>46052</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>84609.970499999996</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="15" customHeight="1">
+    <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>46055</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>66523.528499999986</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15" customHeight="1">
+    <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>46068</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>46776.328499999989</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>46070</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>78567.637499999983</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>46086</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>128067.6375</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>46101</v>
       </c>
@@ -2845,27 +2845,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.23611111111111099" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2879,7 +2879,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF251"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="14" customWidth="1"/>
@@ -2907,40 +2907,40 @@
     <col min="56" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="15" customHeight="1">
-      <c r="C1" s="63" t="s">
+    <row r="1" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="L1" s="64" t="s">
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="L1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="64"/>
-      <c r="Z1" s="64"/>
-      <c r="AA1" s="64"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
-    <row r="2" spans="1:58" ht="29.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+    <row r="2" spans="1:58" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="54" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2964,7 +2964,7 @@
       <c r="I2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="J2" s="54" t="s">
         <v>44</v>
       </c>
       <c r="K2" s="13"/>
@@ -3016,98 +3016,98 @@
       <c r="AA2" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="74" t="s">
+      <c r="AB2" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="AC2" s="67" t="s">
+      <c r="AC2" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="AD2" s="65" t="s">
+      <c r="AD2" s="49" t="s">
         <v>62</v>
       </c>
       <c r="AN2" s="15"/>
       <c r="AO2" s="16"/>
       <c r="AP2" s="15"/>
     </row>
-    <row r="3" spans="1:58" s="18" customFormat="1" ht="27" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="55" t="s">
+    <row r="3" spans="1:58" s="18" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="70" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="F3" s="68" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H3" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="I3" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="J3" s="54"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M3" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="N3" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="O3" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="P3" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="70" t="s">
+      <c r="Q3" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="53" t="s">
+      <c r="R3" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="S3" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="T3" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="53" t="s">
+      <c r="U3" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="Q3" s="53" t="s">
+      <c r="V3" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="R3" s="53" t="s">
+      <c r="W3" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="S3" s="53" t="s">
+      <c r="X3" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="T3" s="53" t="s">
+      <c r="Y3" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="U3" s="53" t="s">
+      <c r="Z3" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="53" t="s">
+      <c r="AA3" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="W3" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y3" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z3" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA3" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3" s="75"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="65"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="49"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="66"/>
+      <c r="AO3" s="50"/>
       <c r="AP3" s="19"/>
       <c r="AS3" s="14"/>
       <c r="AT3" s="14"/>
@@ -3115,39 +3115,39 @@
       <c r="AV3" s="14"/>
       <c r="AW3" s="14"/>
     </row>
-    <row r="4" spans="1:58" s="18" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="57"/>
+    <row r="4" spans="1:58" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="69"/>
-      <c r="AD4" s="65"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="61"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="49"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="66"/>
+      <c r="AO4" s="50"/>
       <c r="AP4" s="19"/>
       <c r="AS4" s="14"/>
       <c r="AT4" s="14"/>
@@ -3155,9 +3155,9 @@
       <c r="AV4" s="14"/>
       <c r="AW4" s="14"/>
     </row>
-    <row r="5" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="5" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B5" s="38">
         <v>110</v>
@@ -3320,9 +3320,9 @@
         <v>353.71</v>
       </c>
     </row>
-    <row r="6" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="6" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B6" s="38">
         <v>12</v>
@@ -3356,7 +3356,7 @@
       <c r="Z6" s="23"/>
       <c r="AA6" s="23"/>
       <c r="AB6" s="24">
-        <f t="shared" ref="AB6:AB69" si="2">L6+M6+P6+Q6+R6+S6+U6+V6+W6+T6+Y6+Z6+AA6</f>
+        <f t="shared" ref="AB6:AB44" si="2">L6+M6+P6+Q6+R6+S6+U6+V6+W6+T6+Y6+Z6+AA6</f>
         <v>0</v>
       </c>
       <c r="AC6" s="24">
@@ -3479,9 +3479,9 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="7" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="7" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B7" s="38">
         <v>3</v>
@@ -3640,9 +3640,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="8" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B8" s="38">
         <v>31</v>
@@ -3801,9 +3801,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="9" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B9" s="38">
         <v>0</v>
@@ -3960,9 +3960,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10" s="38">
         <v>886</v>
@@ -4131,9 +4131,9 @@
         <v>311.22000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B11" s="38">
         <v>0</v>
@@ -4290,9 +4290,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B12" s="38">
         <v>267</v>
@@ -4451,9 +4451,9 @@
         <v>448.56</v>
       </c>
     </row>
-    <row r="13" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B13" s="38">
         <v>0</v>
@@ -4610,9 +4610,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="14" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B14" s="38">
         <v>279</v>
@@ -4771,9 +4771,9 @@
         <v>468.71999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="15" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B15" s="38">
         <v>0</v>
@@ -4936,9 +4936,9 @@
         <v>-897.12</v>
       </c>
     </row>
-    <row r="16" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B16" s="38">
         <v>0</v>
@@ -5095,9 +5095,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="17" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B17" s="38">
         <v>0</v>
@@ -5256,9 +5256,9 @@
         <v>-33.6</v>
       </c>
     </row>
-    <row r="18" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="18" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B18" s="38">
         <v>0</v>
@@ -5415,9 +5415,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="19" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B19" s="38">
         <v>0</v>
@@ -5574,9 +5574,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="20" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B20" s="38">
         <v>0</v>
@@ -5733,9 +5733,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="21" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B21" s="38">
         <v>0</v>
@@ -5892,9 +5892,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="22" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B22" s="38">
         <v>78</v>
@@ -6057,9 +6057,9 @@
         <v>-286.08</v>
       </c>
     </row>
-    <row r="23" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="23" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B23" s="38">
         <v>1</v>
@@ -6220,9 +6220,9 @@
         <v>88.32</v>
       </c>
     </row>
-    <row r="24" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="24" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B24" s="38">
         <v>1</v>
@@ -6395,9 +6395,9 @@
         <v>708.4</v>
       </c>
     </row>
-    <row r="25" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="25" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B25" s="38">
         <v>56</v>
@@ -6558,9 +6558,9 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="26" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="26" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B26" s="38">
         <v>241</v>
@@ -6751,9 +6751,9 @@
         <v>258.39999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="27" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B27" s="38">
         <v>59</v>
@@ -6912,9 +6912,9 @@
         <v>363.87</v>
       </c>
     </row>
-    <row r="28" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B28" s="38">
         <v>0</v>
@@ -6937,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="20">
-        <f t="shared" ref="J6:J69" si="32">B28+E28+F28+G28+H28+I28+C28+D28</f>
+        <f t="shared" ref="J28:J44" si="32">B28+E28+F28+G28+H28+I28+C28+D28</f>
         <v>1322</v>
       </c>
       <c r="K28" s="21"/>
@@ -7093,9 +7093,9 @@
         <v>816.66</v>
       </c>
     </row>
-    <row r="29" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="29" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B29" s="38">
         <v>0</v>
@@ -7260,9 +7260,9 @@
         <v>83.08</v>
       </c>
     </row>
-    <row r="30" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B30" s="38">
         <v>0</v>
@@ -7423,9 +7423,9 @@
         <v>230.48000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="31" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B31" s="38">
         <v>29</v>
@@ -7598,9 +7598,9 @@
         <v>436.76</v>
       </c>
     </row>
-    <row r="32" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="32" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B32" s="38">
         <v>4</v>
@@ -7765,9 +7765,9 @@
         <v>102.75000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="33" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B33" s="38">
         <v>0</v>
@@ -7924,9 +7924,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="34" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B34" s="38">
         <v>0</v>
@@ -8083,9 +8083,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="35" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B35" s="38">
         <v>0</v>
@@ -8242,9 +8242,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B36" s="38">
         <v>0</v>
@@ -8401,9 +8401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="37" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B37" s="38">
         <v>0</v>
@@ -8560,9 +8560,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="38" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B38" s="38">
         <v>430</v>
@@ -8729,9 +8729,9 @@
         <v>38.19</v>
       </c>
     </row>
-    <row r="39" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="39" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B39" s="38">
         <v>0</v>
@@ -8890,9 +8890,9 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="40" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="38" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B40" s="38">
         <v>252</v>
@@ -9067,9 +9067,9 @@
         <v>238.38000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="41" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B41" s="38">
         <v>23</v>
@@ -9228,9 +9228,9 @@
         <v>258.93</v>
       </c>
     </row>
-    <row r="42" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="42" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="38" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B42" s="38">
         <v>0</v>
@@ -9387,9 +9387,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="43" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B43" s="38">
         <v>0</v>
@@ -9546,9 +9546,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="44" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B44" s="38">
         <v>9</v>
@@ -9705,9 +9705,9 @@
         <v>61.83</v>
       </c>
     </row>
-    <row r="45" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="45" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B45" s="38">
         <v>0</v>
@@ -9864,9 +9864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="46" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B46" s="38">
         <v>26</v>
@@ -10025,9 +10025,9 @@
         <v>301.72000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="47" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B47" s="38">
         <v>0</v>
@@ -10184,9 +10184,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="48" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B48" s="38">
         <v>0</v>
@@ -10343,9 +10343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="49" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B49" s="38">
         <v>59</v>
@@ -10504,9 +10504,9 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="50" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="50" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="38" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B50" s="38">
         <v>124</v>
@@ -10671,9 +10671,9 @@
         <v>329.84000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="51" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B51" s="38">
         <v>3</v>
@@ -10830,9 +10830,9 @@
         <v>12.09</v>
       </c>
     </row>
-    <row r="52" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="52" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B52" s="38">
         <v>0</v>
@@ -10995,9 +10995,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="53" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B53" s="38">
         <v>4</v>
@@ -11156,9 +11156,9 @@
         <v>43.28</v>
       </c>
     </row>
-    <row r="54" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="54" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B54" s="38">
         <v>0</v>
@@ -11321,9 +11321,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="55" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B55" s="38">
         <v>171</v>
@@ -11504,9 +11504,9 @@
         <v>2172.7999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="56" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="38" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B56" s="38">
         <v>0</v>
@@ -11663,9 +11663,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="57" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B57" s="38">
         <v>0</v>
@@ -11822,9 +11822,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="58" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B58" s="38">
         <v>0</v>
@@ -11991,9 +11991,9 @@
         <v>580.79999999999995</v>
       </c>
     </row>
-    <row r="59" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="59" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B59" s="38">
         <v>0</v>
@@ -12152,9 +12152,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="60" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B60" s="38">
         <v>0</v>
@@ -12311,9 +12311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="61" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B61" s="38">
         <v>383</v>
@@ -12482,9 +12482,9 @@
         <v>2686.2</v>
       </c>
     </row>
-    <row r="62" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="62" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B62" s="38">
         <v>171</v>
@@ -12665,9 +12665,9 @@
         <v>1804.2</v>
       </c>
     </row>
-    <row r="63" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="63" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B63" s="38">
         <v>0</v>
@@ -12824,9 +12824,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="64" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="38" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B64" s="38">
         <v>0</v>
@@ -12983,9 +12983,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="65" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B65" s="38">
         <v>0</v>
@@ -13152,9 +13152,9 @@
         <v>475.20000000000005</v>
       </c>
     </row>
-    <row r="66" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="66" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="38" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B66" s="38">
         <v>0</v>
@@ -13311,9 +13311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="67" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B67" s="38">
         <v>0</v>
@@ -13470,9 +13470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="68" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="38" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B68" s="38">
         <v>362</v>
@@ -13641,9 +13641,9 @@
         <v>1698.4</v>
       </c>
     </row>
-    <row r="69" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="69" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B69" s="38">
         <v>1</v>
@@ -13800,9 +13800,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="70" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="38" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B70" s="38">
         <v>1</v>
@@ -13959,9 +13959,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="71" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B71" s="38">
         <v>65</v>
@@ -14140,9 +14140,9 @@
         <v>127.28</v>
       </c>
     </row>
-    <row r="72" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="72" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="38" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B72" s="38">
         <v>43</v>
@@ -14315,9 +14315,9 @@
         <v>159.25</v>
       </c>
     </row>
-    <row r="73" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="73" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B73" s="38">
         <v>0</v>
@@ -14474,9 +14474,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="74" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B74" s="38">
         <v>1</v>
@@ -14645,9 +14645,9 @@
         <v>89.6</v>
       </c>
     </row>
-    <row r="75" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="75" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B75" s="38">
         <v>24</v>
@@ -14826,9 +14826,9 @@
         <v>-588</v>
       </c>
     </row>
-    <row r="76" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="76" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="38" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B76" s="38">
         <v>149</v>
@@ -15011,9 +15011,9 @@
         <v>1433.6</v>
       </c>
     </row>
-    <row r="77" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="77" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B77" s="38">
         <v>0</v>
@@ -15170,9 +15170,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="78" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="38" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B78" s="38">
         <v>35</v>
@@ -15335,9 +15335,9 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="79" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="79" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B79" s="38">
         <v>32</v>
@@ -15502,9 +15502,9 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="80" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="80" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="38" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B80" s="38">
         <v>0</v>
@@ -15661,9 +15661,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="81" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="38" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B81" s="38">
         <v>0</v>
@@ -15820,9 +15820,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="82" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="38" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B82" s="38">
         <v>0</v>
@@ -15981,9 +15981,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="83" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="38" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B83" s="38">
         <v>18</v>
@@ -16142,9 +16142,9 @@
         <v>19.440000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="84" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="38" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B84" s="38">
         <v>26</v>
@@ -16311,9 +16311,9 @@
         <v>-17.28</v>
       </c>
     </row>
-    <row r="85" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="85" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="38" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B85" s="38">
         <v>0</v>
@@ -16470,9 +16470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="86" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="38" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B86" s="38">
         <v>0</v>
@@ -16631,9 +16631,9 @@
         <v>-168</v>
       </c>
     </row>
-    <row r="87" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="87" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="38" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B87" s="38">
         <v>10</v>
@@ -16790,9 +16790,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="88" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="88" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B88" s="38">
         <v>152</v>
@@ -16949,9 +16949,9 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="89" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="89" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="38" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B89" s="38">
         <v>1</v>
@@ -17112,9 +17112,9 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="90" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="90" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B90" s="38">
         <v>10</v>
@@ -17275,9 +17275,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="91" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B91" s="38">
         <v>33</v>
@@ -17440,9 +17440,9 @@
         <v>594</v>
       </c>
     </row>
-    <row r="92" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="92" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="38" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B92" s="38">
         <v>18</v>
@@ -17603,9 +17603,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="93" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="38" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B93" s="38">
         <v>66</v>
@@ -17772,9 +17772,9 @@
         <v>577.5</v>
       </c>
     </row>
-    <row r="94" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="94" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="38" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B94" s="38">
         <v>45</v>
@@ -17941,9 +17941,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="95" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="95" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="38" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B95" s="38">
         <v>72</v>
@@ -18108,9 +18108,9 @@
         <v>838.75</v>
       </c>
     </row>
-    <row r="96" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="96" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B96" s="38">
         <v>1</v>
@@ -18271,9 +18271,9 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="97" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="97" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="38" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B97" s="38">
         <v>33</v>
@@ -18438,9 +18438,9 @@
         <v>1433.25</v>
       </c>
     </row>
-    <row r="98" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="98" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B98" s="38">
         <v>32</v>
@@ -18601,9 +18601,9 @@
         <v>360.75</v>
       </c>
     </row>
-    <row r="99" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="99" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B99" s="38">
         <v>4</v>
@@ -18774,9 +18774,9 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="100" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="100" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="38" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B100" s="38">
         <v>19</v>
@@ -18943,9 +18943,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="101" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B101" s="38">
         <v>0</v>
@@ -19112,9 +19112,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="102" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="38" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B102" s="38">
         <v>0</v>
@@ -19273,9 +19273,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="103" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="38" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B103" s="38">
         <v>1</v>
@@ -19444,9 +19444,9 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="104" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="104" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="38" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B104" s="38">
         <v>0</v>
@@ -19621,9 +19621,9 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="105" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="105" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="38" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B105" s="38">
         <v>0</v>
@@ -19782,9 +19782,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="106" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="38" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B106" s="38">
         <v>4</v>
@@ -19949,9 +19949,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="107" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="38" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B107" s="38">
         <v>3</v>
@@ -20126,9 +20126,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="108" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="38" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B108" s="38">
         <v>0</v>
@@ -20287,9 +20287,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="109" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="38" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B109" s="38">
         <v>0</v>
@@ -20456,9 +20456,9 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="110" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="110" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="38" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B110" s="38">
         <v>0</v>
@@ -20615,9 +20615,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="111" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B111" s="38">
         <v>4</v>
@@ -20792,9 +20792,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="112" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="112" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="38" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B112" s="38">
         <v>1</v>
@@ -20971,9 +20971,9 @@
         <v>619.5</v>
       </c>
     </row>
-    <row r="113" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="113" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="38" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B113" s="38">
         <v>159</v>
@@ -21146,9 +21146,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="114" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="38" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B114" s="38">
         <v>98</v>
@@ -21313,9 +21313,9 @@
         <v>604.5</v>
       </c>
     </row>
-    <row r="115" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="115" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="38" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B115" s="38">
         <v>24</v>
@@ -21472,9 +21472,9 @@
         <v>148.80000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="116" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="38" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B116" s="38">
         <v>201</v>
@@ -21631,9 +21631,9 @@
         <v>1869.3000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="117" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="38" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B117" s="38">
         <v>96</v>
@@ -21790,9 +21790,9 @@
         <v>1785.6000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="118" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="38" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B118" s="38">
         <v>7</v>
@@ -21957,9 +21957,9 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="119" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="119" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="38" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B119" s="38">
         <v>0</v>
@@ -22116,9 +22116,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="120" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="38" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B120" s="38">
         <v>0</v>
@@ -22291,9 +22291,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="121" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B121" s="38">
         <v>0</v>
@@ -22456,9 +22456,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="122" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="38" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B122" s="38">
         <v>380</v>
@@ -22641,9 +22641,9 @@
         <v>-1023</v>
       </c>
     </row>
-    <row r="123" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="123" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B123" s="38">
         <v>0</v>
@@ -22812,9 +22812,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="124" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="38" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B124" s="38">
         <v>47</v>
@@ -22977,9 +22977,9 @@
         <v>568.69999999999993</v>
       </c>
     </row>
-    <row r="125" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="125" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B125" s="38">
         <v>219</v>
@@ -23158,9 +23158,9 @@
         <v>3011.25</v>
       </c>
     </row>
-    <row r="126" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="126" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="38" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B126" s="38">
         <v>0</v>
@@ -23323,9 +23323,9 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="127" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="127" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B127" s="38">
         <v>12</v>
@@ -23488,9 +23488,9 @@
         <v>184.8</v>
       </c>
     </row>
-    <row r="128" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="128" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B128" s="38">
         <v>45</v>
@@ -23669,9 +23669,9 @@
         <v>363</v>
       </c>
     </row>
-    <row r="129" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="129" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B129" s="38">
         <v>0</v>
@@ -23828,9 +23828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="130" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="38" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B130" s="38">
         <v>16</v>
@@ -23997,9 +23997,9 @@
         <v>308</v>
       </c>
     </row>
-    <row r="131" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="131" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="38" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B131" s="38">
         <v>0</v>
@@ -24156,9 +24156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="132" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B132" s="38">
         <v>108</v>
@@ -24333,9 +24333,9 @@
         <v>2029.5</v>
       </c>
     </row>
-    <row r="133" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="133" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="38" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B133" s="38">
         <v>0</v>
@@ -24494,9 +24494,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="134" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="38" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B134" s="38">
         <v>0</v>
@@ -24653,9 +24653,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="135" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="38" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B135" s="38">
         <v>2</v>
@@ -24812,9 +24812,9 @@
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="136" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="38" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B136" s="38">
         <v>4</v>
@@ -24971,9 +24971,9 @@
         <v>540</v>
       </c>
     </row>
-    <row r="137" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="137" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="38" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B137" s="38">
         <v>2</v>
@@ -25130,9 +25130,9 @@
         <v>339.6</v>
       </c>
     </row>
-    <row r="138" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="138" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B138" s="38">
         <v>164</v>
@@ -25311,9 +25311,9 @@
         <v>41.36</v>
       </c>
     </row>
-    <row r="139" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="139" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B139" s="38">
         <v>0</v>
@@ -25470,9 +25470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="140" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="38" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B140" s="38">
         <v>0</v>
@@ -25629,9 +25629,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="141" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="38" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B141" s="38">
         <v>0</v>
@@ -25796,9 +25796,9 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="142" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="142" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B142" s="38">
         <v>0</v>
@@ -25955,9 +25955,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="143" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B143" s="38">
         <v>0</v>
@@ -26114,9 +26114,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="144" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="38" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B144" s="38">
         <v>314</v>
@@ -26285,9 +26285,9 @@
         <v>74.36</v>
       </c>
     </row>
-    <row r="145" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="145" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B145" s="38">
         <v>4</v>
@@ -26446,9 +26446,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="146" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="146" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="38" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B146" s="38">
         <v>0</v>
@@ -26609,9 +26609,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="147" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="38" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B147" s="38">
         <v>0</v>
@@ -26768,9 +26768,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="148" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="38" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B148" s="38">
         <v>0</v>
@@ -26933,9 +26933,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="149" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B149" s="38">
         <v>0</v>
@@ -27096,9 +27096,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="150" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="38" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B150" s="38">
         <v>0</v>
@@ -27259,9 +27259,9 @@
         <v>-48</v>
       </c>
     </row>
-    <row r="151" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="151" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="38" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B151" s="38">
         <v>2</v>
@@ -27418,9 +27418,9 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="152" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="152" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="38" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B152" s="38">
         <v>0</v>
@@ -27585,9 +27585,9 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="153" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="153" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="38" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B153" s="38">
         <v>18</v>
@@ -27752,9 +27752,9 @@
         <v>-1632</v>
       </c>
     </row>
-    <row r="154" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="154" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="38" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B154" s="38">
         <v>1644</v>
@@ -27927,9 +27927,9 @@
         <v>2031.1200000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="155" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="38" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B155" s="38">
         <v>0</v>
@@ -28086,9 +28086,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="156" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="38" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B156" s="38">
         <v>0</v>
@@ -28251,9 +28251,9 @@
         <v>271.32</v>
       </c>
     </row>
-    <row r="157" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="157" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="38" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B157" s="38">
         <v>0</v>
@@ -28412,9 +28412,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="158" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="38" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B158" s="38">
         <v>0</v>
@@ -28573,9 +28573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="159" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="38" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B159" s="38">
         <v>0</v>
@@ -28742,9 +28742,9 @@
         <v>226.10000000000002</v>
       </c>
     </row>
-    <row r="160" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="160" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="38" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B160" s="38">
         <v>0</v>
@@ -28907,9 +28907,9 @@
         <v>-127.68</v>
       </c>
     </row>
-    <row r="161" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="161" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="38" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B161" s="38">
         <v>0</v>
@@ -29068,9 +29068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="162" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="38" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B162" s="38">
         <v>0</v>
@@ -29229,9 +29229,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="163" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B163" s="38">
         <v>0</v>
@@ -29390,9 +29390,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="164" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B164" s="38">
         <v>0</v>
@@ -29549,9 +29549,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="165" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="38" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B165" s="38">
         <v>0</v>
@@ -29708,9 +29708,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="166" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="38" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B166" s="38">
         <v>0</v>
@@ -29869,9 +29869,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="167" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="38" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B167" s="38">
         <v>0</v>
@@ -30028,9 +30028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="168" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="38" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B168" s="38">
         <v>3</v>
@@ -30193,9 +30193,9 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="169" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B169" s="38">
         <v>18</v>
@@ -30354,9 +30354,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="170" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="170" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="38" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B170" s="38">
         <v>33</v>
@@ -30515,9 +30515,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="171" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="38" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B171" s="38">
         <v>0</v>
@@ -30674,9 +30674,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="172" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="38" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B172" s="38">
         <v>133</v>
@@ -30849,9 +30849,9 @@
         <v>981.3599999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="173" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="38" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B173" s="38">
         <v>29</v>
@@ -31012,9 +31012,9 @@
         <v>327.12</v>
       </c>
     </row>
-    <row r="174" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="174" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="38" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B174" s="38">
         <v>57</v>
@@ -31191,9 +31191,9 @@
         <v>997.5</v>
       </c>
     </row>
-    <row r="175" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="175" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="38" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B175" s="38">
         <v>0</v>
@@ -31356,9 +31356,9 @@
         <v>-169.73999999999998</v>
       </c>
     </row>
-    <row r="176" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="176" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="38" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B176" s="38">
         <v>0</v>
@@ -31515,9 +31515,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="177" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="38" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B177" s="38">
         <v>21</v>
@@ -31678,9 +31678,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="178" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B178" s="38">
         <v>0</v>
@@ -31837,9 +31837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="179" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B179" s="38">
         <v>0</v>
@@ -31996,9 +31996,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="180" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B180" s="38">
         <v>0</v>
@@ -32157,9 +32157,9 @@
         <v>-82.72</v>
       </c>
     </row>
-    <row r="181" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="181" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="38" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B181" s="38">
         <v>0</v>
@@ -32316,9 +32316,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="182" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B182" s="38">
         <v>8</v>
@@ -32475,9 +32475,9 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="183" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="183" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="38" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B183" s="38">
         <v>0</v>
@@ -32634,9 +32634,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="184" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B184" s="38">
         <v>0</v>
@@ -32793,9 +32793,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="185" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="38" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B185" s="38">
         <v>69</v>
@@ -32956,9 +32956,9 @@
         <v>151.10999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="186" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="38" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B186" s="38">
         <v>0</v>
@@ -33121,9 +33121,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="187" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="38" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B187" s="38">
         <v>0</v>
@@ -33280,9 +33280,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="188" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="38" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B188" s="38">
         <v>0</v>
@@ -33439,9 +33439,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="189" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="38" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B189" s="38">
         <v>0</v>
@@ -33608,9 +33608,9 @@
         <v>-301</v>
       </c>
     </row>
-    <row r="190" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="190" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="38" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B190" s="38">
         <v>0</v>
@@ -33771,9 +33771,9 @@
         <v>1578.96</v>
       </c>
     </row>
-    <row r="191" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="191" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="38" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B191" s="38">
         <v>0</v>
@@ -33936,9 +33936,9 @@
         <v>701.76</v>
       </c>
     </row>
-    <row r="192" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="192" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B192" s="38">
         <v>0</v>
@@ -34099,9 +34099,9 @@
         <v>-264.88</v>
       </c>
     </row>
-    <row r="193" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="193" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="38" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B193" s="38">
         <v>0</v>
@@ -34258,9 +34258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="194" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="38" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B194" s="38">
         <v>0</v>
@@ -34421,9 +34421,9 @@
         <v>-2924</v>
       </c>
     </row>
-    <row r="195" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="195" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="38" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B195" s="38">
         <v>34</v>
@@ -34588,9 +34588,9 @@
         <v>362.70000000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="196" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="38" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B196" s="38">
         <v>23</v>
@@ -34757,9 +34757,9 @@
         <v>169.26000000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="197" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="38" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B197" s="38">
         <v>0</v>
@@ -34918,9 +34918,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="198" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="38" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B198" s="38">
         <v>0</v>
@@ -35079,9 +35079,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="199" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="38" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B199" s="38">
         <v>0</v>
@@ -35240,9 +35240,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="200" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="38" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B200" s="38">
         <v>0</v>
@@ -35401,9 +35401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="201" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="38" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B201" s="38">
         <v>19</v>
@@ -35566,9 +35566,9 @@
         <v>126.9</v>
       </c>
     </row>
-    <row r="202" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="202" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="38" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B202" s="38">
         <v>12</v>
@@ -35731,9 +35731,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="203" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="203" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="38" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B203" s="38">
         <v>8</v>
@@ -35894,9 +35894,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="204" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="204" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="38" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B204" s="38">
         <v>189</v>
@@ -36063,9 +36063,9 @@
         <v>216</v>
       </c>
     </row>
-    <row r="205" spans="1:58" s="37" customFormat="1" ht="15" customHeight="1">
+    <row r="205" spans="1:58" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="38" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B205" s="38">
         <v>1</v>
@@ -36232,9 +36232,9 @@
         <v>-279</v>
       </c>
     </row>
-    <row r="206" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="206" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="38" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B206" s="38">
         <v>380</v>
@@ -36405,9 +36405,9 @@
         <v>1830.6000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="207" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="38" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B207" s="38">
         <v>147</v>
@@ -36572,9 +36572,9 @@
         <v>926.1</v>
       </c>
     </row>
-    <row r="208" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="208" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="38" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B208" s="38">
         <v>347</v>
@@ -36745,9 +36745,9 @@
         <v>2433.6</v>
       </c>
     </row>
-    <row r="209" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="209" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="38" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B209" s="38">
         <v>13</v>
@@ -36910,9 +36910,9 @@
         <v>105.3</v>
       </c>
     </row>
-    <row r="210" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="210" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="38" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B210" s="38">
         <v>1</v>
@@ -37077,9 +37077,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="211" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="38" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B211" s="38">
         <v>0</v>
@@ -37240,9 +37240,9 @@
         <v>485.1</v>
       </c>
     </row>
-    <row r="212" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="212" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="38" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B212" s="38">
         <v>10</v>
@@ -37403,9 +37403,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="213" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="213" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="38" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B213" s="38">
         <v>3</v>
@@ -37566,9 +37566,9 @@
         <v>-23.4</v>
       </c>
     </row>
-    <row r="214" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="214" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="38" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B214" s="38">
         <v>1</v>
@@ -37731,9 +37731,9 @@
         <v>-302.39999999999998</v>
       </c>
     </row>
-    <row r="215" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="215" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="38" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B215" s="38">
         <v>0</v>
@@ -37890,9 +37890,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="216" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="38" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B216" s="38">
         <v>0</v>
@@ -38053,9 +38053,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="217" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="38" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B217" s="38">
         <v>0</v>
@@ -38214,9 +38214,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="218" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="38" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B218" s="38">
         <v>0</v>
@@ -38377,9 +38377,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="219" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="38" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B219" s="38">
         <v>90</v>
@@ -38540,9 +38540,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="220" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="220" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="38" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B220" s="38">
         <v>3</v>
@@ -38703,9 +38703,9 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="221" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="221" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="38" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B221" s="38">
         <v>18</v>
@@ -38864,9 +38864,9 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="222" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="222" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="38" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B222" s="38">
         <v>39</v>
@@ -39031,9 +39031,9 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="223" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="223" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="38" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B223" s="38">
         <v>11</v>
@@ -39196,9 +39196,9 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="224" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="224" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="38" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B224" s="38">
         <v>30</v>
@@ -39363,9 +39363,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="225" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="225" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="38" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B225" s="38">
         <v>48</v>
@@ -39532,9 +39532,9 @@
         <v>302.39999999999998</v>
       </c>
     </row>
-    <row r="226" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="226" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="38" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B226" s="38">
         <v>73</v>
@@ -39695,9 +39695,9 @@
         <v>525.6</v>
       </c>
     </row>
-    <row r="227" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="227" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="38" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B227" s="38">
         <v>5</v>
@@ -39858,9 +39858,9 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="228" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="228" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="38" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B228" s="38">
         <v>3</v>
@@ -40023,9 +40023,9 @@
         <v>-351</v>
       </c>
     </row>
-    <row r="229" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="229" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="38" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B229" s="38">
         <v>0</v>
@@ -40192,9 +40192,9 @@
         <v>485.1</v>
       </c>
     </row>
-    <row r="230" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="230" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="38" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B230" s="38">
         <v>5</v>
@@ -40361,9 +40361,9 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="231" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="231" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="38" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B231" s="38">
         <v>4</v>
@@ -40524,9 +40524,9 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="232" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="232" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="38" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B232" s="38">
         <v>26</v>
@@ -40687,9 +40687,9 @@
         <v>327.59999999999997</v>
       </c>
     </row>
-    <row r="233" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="233" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="38" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B233" s="38">
         <v>2</v>
@@ -40850,9 +40850,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="234" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="234" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="38" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B234" s="38">
         <v>33</v>
@@ -41013,9 +41013,9 @@
         <v>475.2</v>
       </c>
     </row>
-    <row r="235" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="235" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="38" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B235" s="38">
         <v>0</v>
@@ -41174,9 +41174,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="236" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="38" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B236" s="38">
         <v>7</v>
@@ -41335,9 +41335,9 @@
         <v>113.39999999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="237" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="38" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B237" s="38">
         <v>0</v>
@@ -41494,9 +41494,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="238" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="38" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B238" s="38">
         <v>0</v>
@@ -41511,7 +41511,7 @@
       <c r="H238" s="20"/>
       <c r="I238" s="20"/>
       <c r="J238" s="20">
-        <f t="shared" ref="J238:J250" si="126">B238+D238+E238</f>
+        <f t="shared" ref="J238:J249" si="126">B238+D238+E238</f>
         <v>0</v>
       </c>
       <c r="K238" s="21"/>
@@ -41532,7 +41532,7 @@
       <c r="Z238" s="23"/>
       <c r="AA238" s="23"/>
       <c r="AB238" s="24">
-        <f t="shared" ref="AB238:AB250" si="127">L238+M238+P238+Q238+R238</f>
+        <f t="shared" ref="AB238:AB249" si="127">L238+M238+P238+Q238+R238</f>
         <v>0</v>
       </c>
       <c r="AC238" s="24">
@@ -41655,9 +41655,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="239" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="38" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B239" s="38">
         <v>0</v>
@@ -41814,9 +41814,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="240" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="38" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B240" s="38">
         <v>0</v>
@@ -41973,9 +41973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="241" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="38" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B241" s="38">
         <v>0</v>
@@ -42132,9 +42132,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="242" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="38" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B242" s="38">
         <v>1</v>
@@ -42293,9 +42293,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="243" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="243" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="38" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B243" s="38">
         <v>0</v>
@@ -42452,9 +42452,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="244" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="38" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B244" s="38">
         <v>3</v>
@@ -42611,9 +42611,9 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="245" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="245" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="38" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B245" s="38">
         <v>7</v>
@@ -42770,9 +42770,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="246" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="246" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="38" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B246" s="38">
         <v>6</v>
@@ -42931,9 +42931,9 @@
         <v>85.33</v>
       </c>
     </row>
-    <row r="247" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="247" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="38" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B247" s="38">
         <v>0</v>
@@ -43090,9 +43090,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="248" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="38" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B248" s="38">
         <v>0</v>
@@ -43249,9 +43249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="249" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="38" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B249" s="38">
         <v>0</v>
@@ -43408,12 +43408,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="250" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="39" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B250" s="40">
-        <f t="shared" ref="B250:B251" si="128">AE250</f>
+        <f t="shared" ref="B250" si="128">AE250</f>
         <v>56487.819999999992</v>
       </c>
       <c r="C250" s="40">
@@ -43525,119 +43525,119 @@
         <v>43588.159999999989</v>
       </c>
       <c r="AE250" s="25">
-        <f>SUM(AE5:AE249)</f>
+        <f t="shared" ref="AE250:BA250" si="156">SUM(AE5:AE249)</f>
         <v>56487.819999999992</v>
       </c>
       <c r="AF250" s="25">
-        <f>SUM(AF5:AF249)</f>
+        <f t="shared" si="156"/>
         <v>17189.439999999999</v>
       </c>
       <c r="AG250" s="25">
-        <f>SUM(AG5:AG249)</f>
+        <f t="shared" si="156"/>
         <v>831.17000000000007</v>
       </c>
       <c r="AH250" s="25">
-        <f>SUM(AH5:AH249)</f>
+        <f t="shared" si="156"/>
         <v>10126.870000000001</v>
       </c>
       <c r="AI250" s="25">
-        <f>SUM(AI5:AI249)</f>
+        <f t="shared" si="156"/>
         <v>32661.549999999996</v>
       </c>
       <c r="AJ250" s="25">
-        <f>SUM(AJ5:AJ249)</f>
+        <f t="shared" si="156"/>
         <v>3765.18</v>
       </c>
       <c r="AK250" s="25">
-        <f>SUM(AK5:AK249)</f>
+        <f t="shared" si="156"/>
         <v>17726.560000000001</v>
       </c>
       <c r="AL250" s="25">
-        <f>SUM(AL5:AL249)</f>
+        <f t="shared" si="156"/>
         <v>15857.730000000005</v>
       </c>
       <c r="AM250" s="25">
-        <f>SUM(AM5:AM249)</f>
+        <f t="shared" si="156"/>
         <v>75696.620000000039</v>
       </c>
       <c r="AN250" s="25">
-        <f>SUM(AN5:AN249)</f>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="AO250" s="25">
-        <f>SUM(AO5:AO249)</f>
+        <f t="shared" si="156"/>
         <v>6941.9000000000005</v>
       </c>
       <c r="AP250" s="25">
-        <f>SUM(AP5:AP249)</f>
+        <f t="shared" si="156"/>
         <v>2654.6800000000003</v>
       </c>
       <c r="AQ250" s="25">
-        <f>SUM(AQ5:AQ249)</f>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="AR250" s="25">
-        <f>SUM(AR5:AR249)</f>
+        <f t="shared" si="156"/>
         <v>444.72</v>
       </c>
       <c r="AS250" s="25">
-        <f>SUM(AS5:AS249)</f>
+        <f t="shared" si="156"/>
         <v>6004.869999999999</v>
       </c>
       <c r="AT250" s="25">
-        <f>SUM(AT5:AT249)</f>
+        <f t="shared" si="156"/>
         <v>1489.28</v>
       </c>
       <c r="AU250" s="25">
-        <f>SUM(AU5:AU249)</f>
+        <f t="shared" si="156"/>
         <v>7206.3</v>
       </c>
       <c r="AV250" s="25">
-        <f>SUM(AV5:AV249)</f>
+        <f t="shared" si="156"/>
         <v>23458.619999999995</v>
       </c>
       <c r="AW250" s="25">
-        <f>SUM(AW5:AW249)</f>
+        <f t="shared" si="156"/>
         <v>5172.24</v>
       </c>
       <c r="AX250" s="25">
-        <f>SUM(AX5:AX249)</f>
+        <f t="shared" si="156"/>
         <v>9219.2400000000016</v>
       </c>
       <c r="AY250" s="25">
-        <f>SUM(AY5:AY249)</f>
+        <f t="shared" si="156"/>
         <v>7231.57</v>
       </c>
       <c r="AZ250" s="25">
-        <f>SUM(AZ5:AZ249)</f>
+        <f t="shared" si="156"/>
         <v>6886.05</v>
       </c>
       <c r="BA250" s="25">
-        <f>SUM(BA5:BA249)</f>
+        <f t="shared" si="156"/>
         <v>2079.8200000000002</v>
       </c>
       <c r="BB250" s="25">
-        <f t="shared" ref="BB250:BF250" si="156">SUM(BB5:BB249)</f>
+        <f t="shared" ref="BB250:BF250" si="157">SUM(BB5:BB249)</f>
         <v>5804.1</v>
       </c>
       <c r="BC250" s="25">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>2935.23</v>
       </c>
       <c r="BD250" s="25">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>7264.18</v>
       </c>
       <c r="BE250" s="25">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>32108.460000000003</v>
       </c>
       <c r="BF250" s="25">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>43588.159999999989</v>
       </c>
     </row>
-    <row r="251" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
+    <row r="251" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="25" t="s">
         <v>31</v>
       </c>
@@ -43660,6 +43660,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="L1:AA1"/>
     <mergeCell ref="AD2:AD4"/>
@@ -43676,22 +43692,6 @@
     <mergeCell ref="Y3:Y4"/>
     <mergeCell ref="Z3:Z4"/>
     <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <conditionalFormatting sqref="AC5:AD249">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -43712,33 +43712,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A5B878-3B18-453F-B9FC-7ADF8F2BA635}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100493764C60684DF4CB311E8C6DB824A31" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="81926f47a187cc63a92412ba9893c017">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6ddf8778-9569-40ed-9bf8-0f223cbd7521" xmlns:ns3="46728323-6609-471b-b746-bd6c0af0902a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6c744e4b291dae32e38cda089848b113" ns2:_="" ns3:_="">
     <xsd:import namespace="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
@@ -43939,14 +43919,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA7A8F-701B-4BD3-8EBF-76CA05E61F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
+    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
+    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA7A8F-701B-4BD3-8EBF-76CA05E61F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planejamento.xlsx
+++ b/planejamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B8E605-53F7-40C5-AD40-FF7928846F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FA9839-9F7E-4923-B55B-F8257162E329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1081,12 +1081,12 @@
 CHEGADA: 28/03</t>
   </si>
   <si>
-    <t>CONTRATO: 167/2025
-CHEGADA: 31/03</t>
+    <t>CONTRATO: 150/2025
+CHEGADA: 04/04</t>
   </si>
   <si>
-    <t>CONTRATO: 150/2025
-CHEGADA: 04/04</t>
+    <t>CONTRATO: 167/2025
+CHEGADA: 25/03</t>
   </si>
 </sst>
 </file>
@@ -1685,6 +1685,42 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1705,9 +1741,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,53 +1763,20 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2418,8 +2418,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76"/>
-      <c r="B1" s="77" t="s">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2473,88 +2473,88 @@
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="75" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="75" t="s">
+      <c r="K2" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="74" t="s">
+      <c r="L2" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="74" t="s">
+      <c r="M2" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="74" t="s">
+      <c r="O2" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="74" t="s">
+      <c r="P2" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="74" t="s">
+      <c r="Q2" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="74" t="s">
+      <c r="R2" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="74" t="s">
+      <c r="S2" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="74" t="s">
+      <c r="T2" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="74" t="s">
+      <c r="U2" s="77" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
     </row>
     <row r="4" spans="1:21" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -2845,27 +2845,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.23611111111111099" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2908,39 +2908,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="L1" s="48" t="s">
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="L1" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
     </row>
     <row r="2" spans="1:58" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="53" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2964,7 +2964,7 @@
       <c r="I2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="53" t="s">
         <v>44</v>
       </c>
       <c r="K2" s="13"/>
@@ -3016,13 +3016,13 @@
       <c r="AA2" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="59" t="s">
+      <c r="AB2" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AC2" s="51" t="s">
+      <c r="AC2" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="AD2" s="49" t="s">
+      <c r="AD2" s="61" t="s">
         <v>62</v>
       </c>
       <c r="AN2" s="15"/>
@@ -3030,84 +3030,84 @@
       <c r="AP2" s="15"/>
     </row>
     <row r="3" spans="1:58" s="18" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="68" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="55" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="57" t="s">
         <v>331</v>
       </c>
-      <c r="E3" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="G3" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="68" t="s">
+      <c r="I3" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="54"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="66" t="s">
         <v>327</v>
       </c>
-      <c r="M3" s="62" t="s">
+      <c r="M3" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="N3" s="66" t="s">
+      <c r="N3" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="O3" s="66" t="s">
+      <c r="O3" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="Q3" s="62" t="s">
+      <c r="Q3" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="R3" s="62" t="s">
+      <c r="R3" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="S3" s="62" t="s">
+      <c r="S3" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T3" s="62" t="s">
+      <c r="T3" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="W3" s="62" t="s">
+      <c r="W3" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="X3" s="57" t="s">
+      <c r="X3" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="Y3" s="64" t="s">
+      <c r="Y3" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="Z3" s="65" t="s">
+      <c r="Z3" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="AA3" s="65" t="s">
+      <c r="AA3" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="49"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="61"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="50"/>
+      <c r="AO3" s="62"/>
       <c r="AP3" s="19"/>
       <c r="AS3" s="14"/>
       <c r="AT3" s="14"/>
@@ -3116,38 +3116,38 @@
       <c r="AW3" s="14"/>
     </row>
     <row r="4" spans="1:58" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="69"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="49"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="72"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="61"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="50"/>
+      <c r="AO4" s="62"/>
       <c r="AP4" s="19"/>
       <c r="AS4" s="14"/>
       <c r="AT4" s="14"/>
@@ -43660,6 +43660,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="L1:AA1"/>
+    <mergeCell ref="AD2:AD4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="F3:F4"/>
@@ -43676,22 +43692,6 @@
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="L1:AA1"/>
-    <mergeCell ref="AD2:AD4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AC2:AC4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AB2:AB4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
   </mergeCells>
   <conditionalFormatting sqref="AC5:AD249">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -43719,6 +43719,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100493764C60684DF4CB311E8C6DB824A31" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="81926f47a187cc63a92412ba9893c017">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6ddf8778-9569-40ed-9bf8-0f223cbd7521" xmlns:ns3="46728323-6609-471b-b746-bd6c0af0902a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6c744e4b291dae32e38cda089848b113" ns2:_="" ns3:_="">
     <xsd:import namespace="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
@@ -43919,27 +43939,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
+    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA7A8F-701B-4BD3-8EBF-76CA05E61F5F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43956,23 +43975,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
-    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planejamento.xlsx
+++ b/planejamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FA9839-9F7E-4923-B55B-F8257162E329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{647D4157-4CD9-4DB5-AB41-C2E2084F6B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,8 +259,20 @@
 CHEGADA: 05/04</t>
   </si>
   <si>
+    <t>CONTRATO: 150/2025
+CHEGADA: 25/03</t>
+  </si>
+  <si>
     <t>CONTRATO: 160/2025
 CHEGADA: 25/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 146/2025
+CHEGADA: 27/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 167/2025
+CHEGADA: 30/03</t>
   </si>
   <si>
     <t>CONTRATO: 157/2025
@@ -269,6 +281,14 @@
   <si>
     <t>CONTRATO: 126/2025
 CHEGADA: 15/04</t>
+  </si>
+  <si>
+    <t>CONTRATO: 135/2025
+SAÍDA: 28/03</t>
+  </si>
+  <si>
+    <t>CONTRATO: 172/2025
+SAÍDA: 05/04</t>
   </si>
   <si>
     <t>CONTRATO: 171/2025
@@ -292,7 +312,7 @@
   </si>
   <si>
     <t>CONTRATO: XXX/2025
-SAÍDA: 27/03</t>
+SAÍDA: 30/03</t>
   </si>
   <si>
     <t>CONTRATO: 
@@ -1068,26 +1088,6 @@
   <si>
     <t>Peso</t>
   </si>
-  <si>
-    <t>CONTRATO: 135/2025
-SAÍDA: 28/03</t>
-  </si>
-  <si>
-    <t>CONTRATO: 172/2025
-SAÍDA: 02/04</t>
-  </si>
-  <si>
-    <t>CONTRATO: 146/2025
-CHEGADA: 28/03</t>
-  </si>
-  <si>
-    <t>CONTRATO: 150/2025
-CHEGADA: 04/04</t>
-  </si>
-  <si>
-    <t>CONTRATO: 167/2025
-CHEGADA: 25/03</t>
-  </si>
 </sst>
 </file>
 
@@ -1097,7 +1097,7 @@
     <numFmt numFmtId="164" formatCode="d/mmm"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1685,41 +1685,17 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1742,6 +1718,9 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1763,20 +1742,41 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2399,7 +2399,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -2417,9 +2417,9 @@
     <col min="19" max="21" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75" t="s">
+    <row r="1" spans="1:21" ht="37.9" customHeight="1">
+      <c r="A1" s="49"/>
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2472,91 +2472,91 @@
       <c r="T1" s="5"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="76" t="s">
+    <row r="2" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="76" t="s">
+      <c r="H2" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="76" t="s">
+      <c r="I2" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="J2" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="76" t="s">
+      <c r="K2" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="77" t="s">
+      <c r="L2" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="77" t="s">
+      <c r="M2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="77" t="s">
+      <c r="O2" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="77" t="s">
+      <c r="P2" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="77" t="s">
+      <c r="Q2" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="77" t="s">
+      <c r="R2" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="77" t="s">
+      <c r="S2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="77" t="s">
+      <c r="T2" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="77" t="s">
+      <c r="U2" s="47" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
+    <row r="3" spans="1:21" ht="28.5" customHeight="1">
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
     </row>
-    <row r="4" spans="1:21" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="52.9" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>31</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>32</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>11968</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="15" customHeight="1">
       <c r="A8" s="11">
         <v>46015</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>88658.95</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="A9" s="11">
         <v>46020</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>79117.399999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="15" customHeight="1">
       <c r="A10" s="11">
         <v>46027</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>120491.95949999998</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="15" customHeight="1">
       <c r="A11" s="11">
         <v>46029</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>106667.89649999999</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="15" customHeight="1">
       <c r="A12" s="11">
         <v>46030</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>92086.318499999979</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="15" customHeight="1">
       <c r="A13" s="11">
         <v>46034</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>99459.970499999996</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="15" customHeight="1">
       <c r="A14" s="11">
         <v>46052</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>84609.970499999996</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="15" customHeight="1">
       <c r="A15" s="11">
         <v>46055</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>66523.528499999986</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="15" customHeight="1">
       <c r="A16" s="11">
         <v>46068</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>46776.328499999989</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1">
       <c r="A17" s="11">
         <v>46070</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>78567.637499999983</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1">
       <c r="A18" s="11">
         <v>46086</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>128067.6375</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1">
       <c r="A19" s="11">
         <v>46101</v>
       </c>
@@ -2845,27 +2845,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.23611111111111099" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2879,11 +2879,11 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BF251"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="14" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="14" customWidth="1"/>
     <col min="4" max="5" width="14.85546875" style="14" customWidth="1"/>
     <col min="6" max="9" width="12.140625" style="14" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" style="14" customWidth="1"/>
@@ -2907,40 +2907,40 @@
     <col min="56" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="59" t="s">
+    <row r="1" spans="1:58" ht="15" customHeight="1">
+      <c r="C1" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="L1" s="60" t="s">
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="L1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
     </row>
-    <row r="2" spans="1:58" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+    <row r="2" spans="1:58" ht="29.25" customHeight="1">
+      <c r="A2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="58" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2964,7 +2964,7 @@
       <c r="I2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="53" t="s">
+      <c r="J2" s="58" t="s">
         <v>44</v>
       </c>
       <c r="K2" s="13"/>
@@ -3016,98 +3016,98 @@
       <c r="AA2" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="70" t="s">
+      <c r="AB2" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="AC2" s="63" t="s">
+      <c r="AC2" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="AD2" s="61" t="s">
+      <c r="AD2" s="53" t="s">
         <v>62</v>
       </c>
       <c r="AN2" s="15"/>
       <c r="AO2" s="16"/>
       <c r="AP2" s="15"/>
     </row>
-    <row r="3" spans="1:58" s="18" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="51" t="s">
+    <row r="3" spans="1:58" s="18" customFormat="1" ht="27" customHeight="1">
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="57" t="s">
+      <c r="D3" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>331</v>
-      </c>
-      <c r="H3" s="57" t="s">
+      <c r="E3" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="F3" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="53"/>
+      <c r="G3" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="58"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="66" t="s">
-        <v>327</v>
-      </c>
-      <c r="M3" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="N3" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="P3" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q3" s="49" t="s">
+      <c r="L3" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="R3" s="49" t="s">
+      <c r="M3" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="S3" s="49" t="s">
+      <c r="N3" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="T3" s="49" t="s">
+      <c r="O3" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="U3" s="49" t="s">
+      <c r="P3" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="V3" s="49" t="s">
+      <c r="Q3" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="W3" s="49" t="s">
+      <c r="R3" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="S3" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="Y3" s="52" t="s">
+      <c r="T3" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="Z3" s="73" t="s">
+      <c r="U3" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="AA3" s="73" t="s">
+      <c r="V3" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="64"/>
-      <c r="AD3" s="61"/>
+      <c r="W3" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y3" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z3" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA3" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB3" s="64"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="53"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="62"/>
+      <c r="AO3" s="54"/>
       <c r="AP3" s="19"/>
       <c r="AS3" s="14"/>
       <c r="AT3" s="14"/>
@@ -3115,39 +3115,39 @@
       <c r="AV3" s="14"/>
       <c r="AW3" s="14"/>
     </row>
-    <row r="4" spans="1:58" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="53"/>
+    <row r="4" spans="1:58" s="18" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="58"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="72"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="61"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="68"/>
+      <c r="U4" s="68"/>
+      <c r="V4" s="68"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="68"/>
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="57"/>
+      <c r="AD4" s="53"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="62"/>
+      <c r="AO4" s="54"/>
       <c r="AP4" s="19"/>
       <c r="AS4" s="14"/>
       <c r="AT4" s="14"/>
@@ -3155,9 +3155,9 @@
       <c r="AV4" s="14"/>
       <c r="AW4" s="14"/>
     </row>
-    <row r="5" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B5" s="38">
         <v>110</v>
@@ -3320,9 +3320,9 @@
         <v>353.71</v>
       </c>
     </row>
-    <row r="6" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" s="38">
         <v>12</v>
@@ -3356,7 +3356,7 @@
       <c r="Z6" s="23"/>
       <c r="AA6" s="23"/>
       <c r="AB6" s="24">
-        <f t="shared" ref="AB6:AB44" si="2">L6+M6+P6+Q6+R6+S6+U6+V6+W6+T6+Y6+Z6+AA6</f>
+        <f t="shared" ref="AB6:AB69" si="2">L6+M6+P6+Q6+R6+S6+U6+V6+W6+T6+Y6+Z6+AA6</f>
         <v>0</v>
       </c>
       <c r="AC6" s="24">
@@ -3479,9 +3479,9 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="7" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B7" s="38">
         <v>3</v>
@@ -3640,9 +3640,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B8" s="38">
         <v>31</v>
@@ -3801,9 +3801,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="38" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B9" s="38">
         <v>0</v>
@@ -3960,9 +3960,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B10" s="38">
         <v>886</v>
@@ -4131,9 +4131,9 @@
         <v>311.22000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B11" s="38">
         <v>0</v>
@@ -4290,9 +4290,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B12" s="38">
         <v>267</v>
@@ -4451,9 +4451,9 @@
         <v>448.56</v>
       </c>
     </row>
-    <row r="13" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="38" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B13" s="38">
         <v>0</v>
@@ -4610,9 +4610,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="38" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B14" s="38">
         <v>279</v>
@@ -4771,9 +4771,9 @@
         <v>468.71999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B15" s="38">
         <v>0</v>
@@ -4936,9 +4936,9 @@
         <v>-897.12</v>
       </c>
     </row>
-    <row r="16" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B16" s="38">
         <v>0</v>
@@ -5095,9 +5095,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="38" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B17" s="38">
         <v>0</v>
@@ -5256,9 +5256,9 @@
         <v>-33.6</v>
       </c>
     </row>
-    <row r="18" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B18" s="38">
         <v>0</v>
@@ -5415,9 +5415,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B19" s="38">
         <v>0</v>
@@ -5574,9 +5574,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="38" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B20" s="38">
         <v>0</v>
@@ -5733,9 +5733,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B21" s="38">
         <v>0</v>
@@ -5892,9 +5892,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B22" s="38">
         <v>78</v>
@@ -6057,9 +6057,9 @@
         <v>-286.08</v>
       </c>
     </row>
-    <row r="23" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B23" s="38">
         <v>1</v>
@@ -6220,9 +6220,9 @@
         <v>88.32</v>
       </c>
     </row>
-    <row r="24" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B24" s="38">
         <v>1</v>
@@ -6395,9 +6395,9 @@
         <v>708.4</v>
       </c>
     </row>
-    <row r="25" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="38" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B25" s="38">
         <v>56</v>
@@ -6558,9 +6558,9 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="26" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B26" s="38">
         <v>241</v>
@@ -6751,9 +6751,9 @@
         <v>258.39999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="38" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B27" s="38">
         <v>59</v>
@@ -6912,9 +6912,9 @@
         <v>363.87</v>
       </c>
     </row>
-    <row r="28" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B28" s="38">
         <v>0</v>
@@ -6937,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="20">
-        <f t="shared" ref="J28:J44" si="32">B28+E28+F28+G28+H28+I28+C28+D28</f>
+        <f t="shared" ref="J6:J69" si="32">B28+E28+F28+G28+H28+I28+C28+D28</f>
         <v>1322</v>
       </c>
       <c r="K28" s="21"/>
@@ -7093,9 +7093,9 @@
         <v>816.66</v>
       </c>
     </row>
-    <row r="29" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="38" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B29" s="38">
         <v>0</v>
@@ -7260,9 +7260,9 @@
         <v>83.08</v>
       </c>
     </row>
-    <row r="30" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="38" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B30" s="38">
         <v>0</v>
@@ -7423,9 +7423,9 @@
         <v>230.48000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B31" s="38">
         <v>29</v>
@@ -7598,9 +7598,9 @@
         <v>436.76</v>
       </c>
     </row>
-    <row r="32" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="38" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B32" s="38">
         <v>4</v>
@@ -7765,9 +7765,9 @@
         <v>102.75000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="38" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B33" s="38">
         <v>0</v>
@@ -7924,9 +7924,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="38" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B34" s="38">
         <v>0</v>
@@ -8083,9 +8083,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="38" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B35" s="38">
         <v>0</v>
@@ -8242,9 +8242,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="38" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B36" s="38">
         <v>0</v>
@@ -8401,9 +8401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="38" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B37" s="38">
         <v>0</v>
@@ -8560,9 +8560,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="38" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B38" s="38">
         <v>430</v>
@@ -8729,9 +8729,9 @@
         <v>38.19</v>
       </c>
     </row>
-    <row r="39" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="38" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B39" s="38">
         <v>0</v>
@@ -8890,9 +8890,9 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B40" s="38">
         <v>252</v>
@@ -9067,9 +9067,9 @@
         <v>238.38000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B41" s="38">
         <v>23</v>
@@ -9228,9 +9228,9 @@
         <v>258.93</v>
       </c>
     </row>
-    <row r="42" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B42" s="38">
         <v>0</v>
@@ -9387,9 +9387,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="38" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B43" s="38">
         <v>0</v>
@@ -9546,9 +9546,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="38" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B44" s="38">
         <v>9</v>
@@ -9705,9 +9705,9 @@
         <v>61.83</v>
       </c>
     </row>
-    <row r="45" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="38" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B45" s="38">
         <v>0</v>
@@ -9864,9 +9864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="38" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B46" s="38">
         <v>26</v>
@@ -10025,9 +10025,9 @@
         <v>301.72000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="38" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B47" s="38">
         <v>0</v>
@@ -10184,9 +10184,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="38" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B48" s="38">
         <v>0</v>
@@ -10343,9 +10343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="38" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B49" s="38">
         <v>59</v>
@@ -10504,9 +10504,9 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="50" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="38" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B50" s="38">
         <v>124</v>
@@ -10671,9 +10671,9 @@
         <v>329.84000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="38" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B51" s="38">
         <v>3</v>
@@ -10830,9 +10830,9 @@
         <v>12.09</v>
       </c>
     </row>
-    <row r="52" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B52" s="38">
         <v>0</v>
@@ -10995,9 +10995,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="38" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B53" s="38">
         <v>4</v>
@@ -11156,9 +11156,9 @@
         <v>43.28</v>
       </c>
     </row>
-    <row r="54" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B54" s="38">
         <v>0</v>
@@ -11321,9 +11321,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="38" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B55" s="38">
         <v>171</v>
@@ -11504,9 +11504,9 @@
         <v>2172.7999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="38" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B56" s="38">
         <v>0</v>
@@ -11663,9 +11663,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="38" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B57" s="38">
         <v>0</v>
@@ -11822,9 +11822,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="38" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B58" s="38">
         <v>0</v>
@@ -11991,9 +11991,9 @@
         <v>580.79999999999995</v>
       </c>
     </row>
-    <row r="59" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B59" s="38">
         <v>0</v>
@@ -12152,9 +12152,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="38" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B60" s="38">
         <v>0</v>
@@ -12311,9 +12311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B61" s="38">
         <v>383</v>
@@ -12482,9 +12482,9 @@
         <v>2686.2</v>
       </c>
     </row>
-    <row r="62" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="38" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B62" s="38">
         <v>171</v>
@@ -12665,9 +12665,9 @@
         <v>1804.2</v>
       </c>
     </row>
-    <row r="63" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="38" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B63" s="38">
         <v>0</v>
@@ -12824,9 +12824,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="38" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B64" s="38">
         <v>0</v>
@@ -12983,9 +12983,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="38" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B65" s="38">
         <v>0</v>
@@ -13152,9 +13152,9 @@
         <v>475.20000000000005</v>
       </c>
     </row>
-    <row r="66" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="38" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B66" s="38">
         <v>0</v>
@@ -13311,9 +13311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="38" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B67" s="38">
         <v>0</v>
@@ -13470,9 +13470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="38" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B68" s="38">
         <v>362</v>
@@ -13641,9 +13641,9 @@
         <v>1698.4</v>
       </c>
     </row>
-    <row r="69" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="38" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B69" s="38">
         <v>1</v>
@@ -13800,9 +13800,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="38" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B70" s="38">
         <v>1</v>
@@ -13959,9 +13959,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="38" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B71" s="38">
         <v>65</v>
@@ -14140,9 +14140,9 @@
         <v>127.28</v>
       </c>
     </row>
-    <row r="72" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="38" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B72" s="38">
         <v>43</v>
@@ -14315,9 +14315,9 @@
         <v>159.25</v>
       </c>
     </row>
-    <row r="73" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="38" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B73" s="38">
         <v>0</v>
@@ -14474,9 +14474,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="38" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B74" s="38">
         <v>1</v>
@@ -14645,9 +14645,9 @@
         <v>89.6</v>
       </c>
     </row>
-    <row r="75" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="38" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B75" s="38">
         <v>24</v>
@@ -14826,9 +14826,9 @@
         <v>-588</v>
       </c>
     </row>
-    <row r="76" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B76" s="38">
         <v>149</v>
@@ -15011,9 +15011,9 @@
         <v>1433.6</v>
       </c>
     </row>
-    <row r="77" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="38" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B77" s="38">
         <v>0</v>
@@ -15170,9 +15170,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="38" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B78" s="38">
         <v>35</v>
@@ -15335,9 +15335,9 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="79" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="38" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B79" s="38">
         <v>32</v>
@@ -15502,9 +15502,9 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="80" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="38" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B80" s="38">
         <v>0</v>
@@ -15661,9 +15661,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="38" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B81" s="38">
         <v>0</v>
@@ -15820,9 +15820,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="38" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B82" s="38">
         <v>0</v>
@@ -15981,9 +15981,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="38" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B83" s="38">
         <v>18</v>
@@ -16142,9 +16142,9 @@
         <v>19.440000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="38" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B84" s="38">
         <v>26</v>
@@ -16311,9 +16311,9 @@
         <v>-17.28</v>
       </c>
     </row>
-    <row r="85" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="38" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B85" s="38">
         <v>0</v>
@@ -16470,9 +16470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="38" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B86" s="38">
         <v>0</v>
@@ -16631,9 +16631,9 @@
         <v>-168</v>
       </c>
     </row>
-    <row r="87" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="38" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B87" s="38">
         <v>10</v>
@@ -16790,9 +16790,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="88" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="38" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B88" s="38">
         <v>152</v>
@@ -16949,9 +16949,9 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="89" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="38" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B89" s="38">
         <v>1</v>
@@ -17112,9 +17112,9 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="90" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="38" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B90" s="38">
         <v>10</v>
@@ -17275,9 +17275,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="38" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B91" s="38">
         <v>33</v>
@@ -17440,9 +17440,9 @@
         <v>594</v>
       </c>
     </row>
-    <row r="92" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="38" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B92" s="38">
         <v>18</v>
@@ -17603,9 +17603,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="38" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B93" s="38">
         <v>66</v>
@@ -17772,9 +17772,9 @@
         <v>577.5</v>
       </c>
     </row>
-    <row r="94" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="38" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B94" s="38">
         <v>45</v>
@@ -17941,9 +17941,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="95" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="38" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B95" s="38">
         <v>72</v>
@@ -18108,9 +18108,9 @@
         <v>838.75</v>
       </c>
     </row>
-    <row r="96" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="38" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B96" s="38">
         <v>1</v>
@@ -18271,9 +18271,9 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="97" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="38" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B97" s="38">
         <v>33</v>
@@ -18438,9 +18438,9 @@
         <v>1433.25</v>
       </c>
     </row>
-    <row r="98" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="38" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B98" s="38">
         <v>32</v>
@@ -18601,9 +18601,9 @@
         <v>360.75</v>
       </c>
     </row>
-    <row r="99" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="38" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B99" s="38">
         <v>4</v>
@@ -18774,9 +18774,9 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="100" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="38" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B100" s="38">
         <v>19</v>
@@ -18943,9 +18943,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="38" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B101" s="38">
         <v>0</v>
@@ -19112,9 +19112,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="38" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B102" s="38">
         <v>0</v>
@@ -19273,9 +19273,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="38" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B103" s="38">
         <v>1</v>
@@ -19444,9 +19444,9 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="104" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="38" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B104" s="38">
         <v>0</v>
@@ -19621,9 +19621,9 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="105" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="38" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B105" s="38">
         <v>0</v>
@@ -19782,9 +19782,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="38" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B106" s="38">
         <v>4</v>
@@ -19949,9 +19949,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="38" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B107" s="38">
         <v>3</v>
@@ -20126,9 +20126,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="38" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B108" s="38">
         <v>0</v>
@@ -20287,9 +20287,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="38" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B109" s="38">
         <v>0</v>
@@ -20456,9 +20456,9 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="110" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="38" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B110" s="38">
         <v>0</v>
@@ -20615,9 +20615,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B111" s="38">
         <v>4</v>
@@ -20792,9 +20792,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="112" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="38" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B112" s="38">
         <v>1</v>
@@ -20971,9 +20971,9 @@
         <v>619.5</v>
       </c>
     </row>
-    <row r="113" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="38" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B113" s="38">
         <v>159</v>
@@ -21146,9 +21146,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A114" s="38" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B114" s="38">
         <v>98</v>
@@ -21313,9 +21313,9 @@
         <v>604.5</v>
       </c>
     </row>
-    <row r="115" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="38" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B115" s="38">
         <v>24</v>
@@ -21472,9 +21472,9 @@
         <v>148.80000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A116" s="38" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B116" s="38">
         <v>201</v>
@@ -21631,9 +21631,9 @@
         <v>1869.3000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="38" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B117" s="38">
         <v>96</v>
@@ -21790,9 +21790,9 @@
         <v>1785.6000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="38" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B118" s="38">
         <v>7</v>
@@ -21957,9 +21957,9 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="119" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="38" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B119" s="38">
         <v>0</v>
@@ -22116,9 +22116,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="38" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B120" s="38">
         <v>0</v>
@@ -22291,9 +22291,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="38" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B121" s="38">
         <v>0</v>
@@ -22456,9 +22456,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="38" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B122" s="38">
         <v>380</v>
@@ -22641,9 +22641,9 @@
         <v>-1023</v>
       </c>
     </row>
-    <row r="123" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A123" s="38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B123" s="38">
         <v>0</v>
@@ -22812,9 +22812,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A124" s="38" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B124" s="38">
         <v>47</v>
@@ -22977,9 +22977,9 @@
         <v>568.69999999999993</v>
       </c>
     </row>
-    <row r="125" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="38" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B125" s="38">
         <v>219</v>
@@ -23158,9 +23158,9 @@
         <v>3011.25</v>
       </c>
     </row>
-    <row r="126" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="38" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B126" s="38">
         <v>0</v>
@@ -23323,9 +23323,9 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="127" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="38" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B127" s="38">
         <v>12</v>
@@ -23488,9 +23488,9 @@
         <v>184.8</v>
       </c>
     </row>
-    <row r="128" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="38" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B128" s="38">
         <v>45</v>
@@ -23669,9 +23669,9 @@
         <v>363</v>
       </c>
     </row>
-    <row r="129" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="38" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B129" s="38">
         <v>0</v>
@@ -23828,9 +23828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A130" s="38" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B130" s="38">
         <v>16</v>
@@ -23997,9 +23997,9 @@
         <v>308</v>
       </c>
     </row>
-    <row r="131" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="38" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B131" s="38">
         <v>0</v>
@@ -24156,9 +24156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A132" s="38" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B132" s="38">
         <v>108</v>
@@ -24333,9 +24333,9 @@
         <v>2029.5</v>
       </c>
     </row>
-    <row r="133" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A133" s="38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B133" s="38">
         <v>0</v>
@@ -24494,9 +24494,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A134" s="38" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B134" s="38">
         <v>0</v>
@@ -24653,9 +24653,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="38" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B135" s="38">
         <v>2</v>
@@ -24812,9 +24812,9 @@
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A136" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B136" s="38">
         <v>4</v>
@@ -24971,9 +24971,9 @@
         <v>540</v>
       </c>
     </row>
-    <row r="137" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="38" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B137" s="38">
         <v>2</v>
@@ -25130,9 +25130,9 @@
         <v>339.6</v>
       </c>
     </row>
-    <row r="138" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A138" s="38" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B138" s="38">
         <v>164</v>
@@ -25311,9 +25311,9 @@
         <v>41.36</v>
       </c>
     </row>
-    <row r="139" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A139" s="38" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B139" s="38">
         <v>0</v>
@@ -25470,9 +25470,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A140" s="38" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B140" s="38">
         <v>0</v>
@@ -25629,9 +25629,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="38" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B141" s="38">
         <v>0</v>
@@ -25796,9 +25796,9 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="142" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="38" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B142" s="38">
         <v>0</v>
@@ -25955,9 +25955,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A143" s="38" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B143" s="38">
         <v>0</v>
@@ -26114,9 +26114,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A144" s="38" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B144" s="38">
         <v>314</v>
@@ -26285,9 +26285,9 @@
         <v>74.36</v>
       </c>
     </row>
-    <row r="145" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A145" s="38" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B145" s="38">
         <v>4</v>
@@ -26446,9 +26446,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="146" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A146" s="38" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B146" s="38">
         <v>0</v>
@@ -26609,9 +26609,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A147" s="38" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B147" s="38">
         <v>0</v>
@@ -26768,9 +26768,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A148" s="38" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B148" s="38">
         <v>0</v>
@@ -26933,9 +26933,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A149" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B149" s="38">
         <v>0</v>
@@ -27096,9 +27096,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A150" s="38" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B150" s="38">
         <v>0</v>
@@ -27259,9 +27259,9 @@
         <v>-48</v>
       </c>
     </row>
-    <row r="151" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="38" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B151" s="38">
         <v>2</v>
@@ -27418,9 +27418,9 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="152" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="38" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B152" s="38">
         <v>0</v>
@@ -27585,9 +27585,9 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="153" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="38" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B153" s="38">
         <v>18</v>
@@ -27752,9 +27752,9 @@
         <v>-1632</v>
       </c>
     </row>
-    <row r="154" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="38" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B154" s="38">
         <v>1644</v>
@@ -27927,9 +27927,9 @@
         <v>2031.1200000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="38" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B155" s="38">
         <v>0</v>
@@ -28086,9 +28086,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="38" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B156" s="38">
         <v>0</v>
@@ -28251,9 +28251,9 @@
         <v>271.32</v>
       </c>
     </row>
-    <row r="157" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="38" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B157" s="38">
         <v>0</v>
@@ -28412,9 +28412,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="38" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B158" s="38">
         <v>0</v>
@@ -28573,9 +28573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="38" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B159" s="38">
         <v>0</v>
@@ -28742,9 +28742,9 @@
         <v>226.10000000000002</v>
       </c>
     </row>
-    <row r="160" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="38" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B160" s="38">
         <v>0</v>
@@ -28907,9 +28907,9 @@
         <v>-127.68</v>
       </c>
     </row>
-    <row r="161" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A161" s="38" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B161" s="38">
         <v>0</v>
@@ -29068,9 +29068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A162" s="38" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B162" s="38">
         <v>0</v>
@@ -29229,9 +29229,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A163" s="38" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B163" s="38">
         <v>0</v>
@@ -29390,9 +29390,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A164" s="38" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B164" s="38">
         <v>0</v>
@@ -29549,9 +29549,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A165" s="38" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B165" s="38">
         <v>0</v>
@@ -29708,9 +29708,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A166" s="38" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B166" s="38">
         <v>0</v>
@@ -29869,9 +29869,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="38" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B167" s="38">
         <v>0</v>
@@ -30028,9 +30028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="38" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B168" s="38">
         <v>3</v>
@@ -30193,9 +30193,9 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="38" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B169" s="38">
         <v>18</v>
@@ -30354,9 +30354,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="170" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="38" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B170" s="38">
         <v>33</v>
@@ -30515,9 +30515,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="38" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B171" s="38">
         <v>0</v>
@@ -30674,9 +30674,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="38" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B172" s="38">
         <v>133</v>
@@ -30849,9 +30849,9 @@
         <v>981.3599999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="38" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B173" s="38">
         <v>29</v>
@@ -31012,9 +31012,9 @@
         <v>327.12</v>
       </c>
     </row>
-    <row r="174" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="38" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B174" s="38">
         <v>57</v>
@@ -31191,9 +31191,9 @@
         <v>997.5</v>
       </c>
     </row>
-    <row r="175" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="38" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B175" s="38">
         <v>0</v>
@@ -31356,9 +31356,9 @@
         <v>-169.73999999999998</v>
       </c>
     </row>
-    <row r="176" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="38" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B176" s="38">
         <v>0</v>
@@ -31515,9 +31515,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="38" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B177" s="38">
         <v>21</v>
@@ -31678,9 +31678,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="38" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B178" s="38">
         <v>0</v>
@@ -31837,9 +31837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="38" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B179" s="38">
         <v>0</v>
@@ -31996,9 +31996,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="38" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B180" s="38">
         <v>0</v>
@@ -32157,9 +32157,9 @@
         <v>-82.72</v>
       </c>
     </row>
-    <row r="181" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="38" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B181" s="38">
         <v>0</v>
@@ -32316,9 +32316,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="38" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B182" s="38">
         <v>8</v>
@@ -32475,9 +32475,9 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="183" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="38" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B183" s="38">
         <v>0</v>
@@ -32634,9 +32634,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="38" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B184" s="38">
         <v>0</v>
@@ -32793,9 +32793,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="38" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B185" s="38">
         <v>69</v>
@@ -32956,9 +32956,9 @@
         <v>151.10999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="38" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B186" s="38">
         <v>0</v>
@@ -33121,9 +33121,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="38" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B187" s="38">
         <v>0</v>
@@ -33280,9 +33280,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="38" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B188" s="38">
         <v>0</v>
@@ -33439,9 +33439,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="38" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B189" s="38">
         <v>0</v>
@@ -33608,9 +33608,9 @@
         <v>-301</v>
       </c>
     </row>
-    <row r="190" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="38" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B190" s="38">
         <v>0</v>
@@ -33771,9 +33771,9 @@
         <v>1578.96</v>
       </c>
     </row>
-    <row r="191" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="38" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B191" s="38">
         <v>0</v>
@@ -33936,9 +33936,9 @@
         <v>701.76</v>
       </c>
     </row>
-    <row r="192" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="38" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B192" s="38">
         <v>0</v>
@@ -34099,9 +34099,9 @@
         <v>-264.88</v>
       </c>
     </row>
-    <row r="193" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="38" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B193" s="38">
         <v>0</v>
@@ -34258,9 +34258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="38" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B194" s="38">
         <v>0</v>
@@ -34421,9 +34421,9 @@
         <v>-2924</v>
       </c>
     </row>
-    <row r="195" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A195" s="38" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B195" s="38">
         <v>34</v>
@@ -34588,9 +34588,9 @@
         <v>362.70000000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A196" s="38" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B196" s="38">
         <v>23</v>
@@ -34757,9 +34757,9 @@
         <v>169.26000000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A197" s="38" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B197" s="38">
         <v>0</v>
@@ -34918,9 +34918,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A198" s="38" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B198" s="38">
         <v>0</v>
@@ -35079,9 +35079,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A199" s="38" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B199" s="38">
         <v>0</v>
@@ -35240,9 +35240,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A200" s="38" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B200" s="38">
         <v>0</v>
@@ -35401,9 +35401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A201" s="38" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B201" s="38">
         <v>19</v>
@@ -35566,9 +35566,9 @@
         <v>126.9</v>
       </c>
     </row>
-    <row r="202" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A202" s="38" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B202" s="38">
         <v>12</v>
@@ -35731,9 +35731,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="203" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A203" s="38" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B203" s="38">
         <v>8</v>
@@ -35894,9 +35894,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="204" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A204" s="38" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B204" s="38">
         <v>189</v>
@@ -36063,9 +36063,9 @@
         <v>216</v>
       </c>
     </row>
-    <row r="205" spans="1:58" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:58" s="37" customFormat="1" ht="15" customHeight="1">
       <c r="A205" s="38" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B205" s="38">
         <v>1</v>
@@ -36232,9 +36232,9 @@
         <v>-279</v>
       </c>
     </row>
-    <row r="206" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A206" s="38" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B206" s="38">
         <v>380</v>
@@ -36405,9 +36405,9 @@
         <v>1830.6000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A207" s="38" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B207" s="38">
         <v>147</v>
@@ -36572,9 +36572,9 @@
         <v>926.1</v>
       </c>
     </row>
-    <row r="208" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A208" s="38" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B208" s="38">
         <v>347</v>
@@ -36745,9 +36745,9 @@
         <v>2433.6</v>
       </c>
     </row>
-    <row r="209" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A209" s="38" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B209" s="38">
         <v>13</v>
@@ -36910,9 +36910,9 @@
         <v>105.3</v>
       </c>
     </row>
-    <row r="210" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A210" s="38" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B210" s="38">
         <v>1</v>
@@ -37077,9 +37077,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A211" s="38" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B211" s="38">
         <v>0</v>
@@ -37240,9 +37240,9 @@
         <v>485.1</v>
       </c>
     </row>
-    <row r="212" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A212" s="38" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B212" s="38">
         <v>10</v>
@@ -37403,9 +37403,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="213" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="38" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B213" s="38">
         <v>3</v>
@@ -37566,9 +37566,9 @@
         <v>-23.4</v>
       </c>
     </row>
-    <row r="214" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A214" s="38" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B214" s="38">
         <v>1</v>
@@ -37731,9 +37731,9 @@
         <v>-302.39999999999998</v>
       </c>
     </row>
-    <row r="215" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A215" s="38" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B215" s="38">
         <v>0</v>
@@ -37890,9 +37890,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A216" s="38" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B216" s="38">
         <v>0</v>
@@ -38053,9 +38053,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A217" s="38" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B217" s="38">
         <v>0</v>
@@ -38214,9 +38214,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A218" s="38" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B218" s="38">
         <v>0</v>
@@ -38377,9 +38377,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A219" s="38" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B219" s="38">
         <v>90</v>
@@ -38540,9 +38540,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="220" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A220" s="38" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B220" s="38">
         <v>3</v>
@@ -38703,9 +38703,9 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="221" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A221" s="38" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B221" s="38">
         <v>18</v>
@@ -38864,9 +38864,9 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="222" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A222" s="38" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B222" s="38">
         <v>39</v>
@@ -39031,9 +39031,9 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="223" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A223" s="38" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B223" s="38">
         <v>11</v>
@@ -39196,9 +39196,9 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="224" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A224" s="38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B224" s="38">
         <v>30</v>
@@ -39363,9 +39363,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="225" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A225" s="38" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B225" s="38">
         <v>48</v>
@@ -39532,9 +39532,9 @@
         <v>302.39999999999998</v>
       </c>
     </row>
-    <row r="226" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A226" s="38" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B226" s="38">
         <v>73</v>
@@ -39695,9 +39695,9 @@
         <v>525.6</v>
       </c>
     </row>
-    <row r="227" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A227" s="38" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B227" s="38">
         <v>5</v>
@@ -39858,9 +39858,9 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="228" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A228" s="38" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B228" s="38">
         <v>3</v>
@@ -40023,9 +40023,9 @@
         <v>-351</v>
       </c>
     </row>
-    <row r="229" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A229" s="38" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B229" s="38">
         <v>0</v>
@@ -40192,9 +40192,9 @@
         <v>485.1</v>
       </c>
     </row>
-    <row r="230" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A230" s="38" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B230" s="38">
         <v>5</v>
@@ -40361,9 +40361,9 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="231" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A231" s="38" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B231" s="38">
         <v>4</v>
@@ -40524,9 +40524,9 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="232" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A232" s="38" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B232" s="38">
         <v>26</v>
@@ -40687,9 +40687,9 @@
         <v>327.59999999999997</v>
       </c>
     </row>
-    <row r="233" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A233" s="38" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B233" s="38">
         <v>2</v>
@@ -40850,9 +40850,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="234" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A234" s="38" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B234" s="38">
         <v>33</v>
@@ -41013,9 +41013,9 @@
         <v>475.2</v>
       </c>
     </row>
-    <row r="235" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A235" s="38" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B235" s="38">
         <v>0</v>
@@ -41174,9 +41174,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A236" s="38" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B236" s="38">
         <v>7</v>
@@ -41335,9 +41335,9 @@
         <v>113.39999999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A237" s="38" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B237" s="38">
         <v>0</v>
@@ -41494,9 +41494,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A238" s="38" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B238" s="38">
         <v>0</v>
@@ -41511,7 +41511,7 @@
       <c r="H238" s="20"/>
       <c r="I238" s="20"/>
       <c r="J238" s="20">
-        <f t="shared" ref="J238:J249" si="126">B238+D238+E238</f>
+        <f t="shared" ref="J238:J250" si="126">B238+D238+E238</f>
         <v>0</v>
       </c>
       <c r="K238" s="21"/>
@@ -41532,7 +41532,7 @@
       <c r="Z238" s="23"/>
       <c r="AA238" s="23"/>
       <c r="AB238" s="24">
-        <f t="shared" ref="AB238:AB249" si="127">L238+M238+P238+Q238+R238</f>
+        <f t="shared" ref="AB238:AB250" si="127">L238+M238+P238+Q238+R238</f>
         <v>0</v>
       </c>
       <c r="AC238" s="24">
@@ -41655,9 +41655,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A239" s="38" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B239" s="38">
         <v>0</v>
@@ -41814,9 +41814,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A240" s="38" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B240" s="38">
         <v>0</v>
@@ -41973,9 +41973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A241" s="38" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B241" s="38">
         <v>0</v>
@@ -42132,9 +42132,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A242" s="38" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B242" s="38">
         <v>1</v>
@@ -42293,9 +42293,9 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="243" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A243" s="38" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B243" s="38">
         <v>0</v>
@@ -42452,9 +42452,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A244" s="38" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B244" s="38">
         <v>3</v>
@@ -42611,9 +42611,9 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="245" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A245" s="38" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B245" s="38">
         <v>7</v>
@@ -42770,9 +42770,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="246" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A246" s="38" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B246" s="38">
         <v>6</v>
@@ -42931,9 +42931,9 @@
         <v>85.33</v>
       </c>
     </row>
-    <row r="247" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A247" s="38" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B247" s="38">
         <v>0</v>
@@ -43090,9 +43090,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A248" s="38" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B248" s="38">
         <v>0</v>
@@ -43249,9 +43249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A249" s="38" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B249" s="38">
         <v>0</v>
@@ -43408,12 +43408,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A250" s="39" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B250" s="40">
-        <f t="shared" ref="B250" si="128">AE250</f>
+        <f t="shared" ref="B250:B251" si="128">AE250</f>
         <v>56487.819999999992</v>
       </c>
       <c r="C250" s="40">
@@ -43525,119 +43525,119 @@
         <v>43588.159999999989</v>
       </c>
       <c r="AE250" s="25">
-        <f t="shared" ref="AE250:BA250" si="156">SUM(AE5:AE249)</f>
+        <f>SUM(AE5:AE249)</f>
         <v>56487.819999999992</v>
       </c>
       <c r="AF250" s="25">
+        <f>SUM(AF5:AF249)</f>
+        <v>17189.439999999999</v>
+      </c>
+      <c r="AG250" s="25">
+        <f>SUM(AG5:AG249)</f>
+        <v>831.17000000000007</v>
+      </c>
+      <c r="AH250" s="25">
+        <f>SUM(AH5:AH249)</f>
+        <v>10126.870000000001</v>
+      </c>
+      <c r="AI250" s="25">
+        <f>SUM(AI5:AI249)</f>
+        <v>32661.549999999996</v>
+      </c>
+      <c r="AJ250" s="25">
+        <f>SUM(AJ5:AJ249)</f>
+        <v>3765.18</v>
+      </c>
+      <c r="AK250" s="25">
+        <f>SUM(AK5:AK249)</f>
+        <v>17726.560000000001</v>
+      </c>
+      <c r="AL250" s="25">
+        <f>SUM(AL5:AL249)</f>
+        <v>15857.730000000005</v>
+      </c>
+      <c r="AM250" s="25">
+        <f>SUM(AM5:AM249)</f>
+        <v>75696.620000000039</v>
+      </c>
+      <c r="AN250" s="25">
+        <f>SUM(AN5:AN249)</f>
+        <v>0</v>
+      </c>
+      <c r="AO250" s="25">
+        <f>SUM(AO5:AO249)</f>
+        <v>6941.9000000000005</v>
+      </c>
+      <c r="AP250" s="25">
+        <f>SUM(AP5:AP249)</f>
+        <v>2654.6800000000003</v>
+      </c>
+      <c r="AQ250" s="25">
+        <f>SUM(AQ5:AQ249)</f>
+        <v>0</v>
+      </c>
+      <c r="AR250" s="25">
+        <f>SUM(AR5:AR249)</f>
+        <v>444.72</v>
+      </c>
+      <c r="AS250" s="25">
+        <f>SUM(AS5:AS249)</f>
+        <v>6004.869999999999</v>
+      </c>
+      <c r="AT250" s="25">
+        <f>SUM(AT5:AT249)</f>
+        <v>1489.28</v>
+      </c>
+      <c r="AU250" s="25">
+        <f>SUM(AU5:AU249)</f>
+        <v>7206.3</v>
+      </c>
+      <c r="AV250" s="25">
+        <f>SUM(AV5:AV249)</f>
+        <v>23458.619999999995</v>
+      </c>
+      <c r="AW250" s="25">
+        <f>SUM(AW5:AW249)</f>
+        <v>5172.24</v>
+      </c>
+      <c r="AX250" s="25">
+        <f>SUM(AX5:AX249)</f>
+        <v>9219.2400000000016</v>
+      </c>
+      <c r="AY250" s="25">
+        <f>SUM(AY5:AY249)</f>
+        <v>7231.57</v>
+      </c>
+      <c r="AZ250" s="25">
+        <f>SUM(AZ5:AZ249)</f>
+        <v>6886.05</v>
+      </c>
+      <c r="BA250" s="25">
+        <f>SUM(BA5:BA249)</f>
+        <v>2079.8200000000002</v>
+      </c>
+      <c r="BB250" s="25">
+        <f t="shared" ref="BB250:BF250" si="156">SUM(BB5:BB249)</f>
+        <v>5804.1</v>
+      </c>
+      <c r="BC250" s="25">
         <f t="shared" si="156"/>
-        <v>17189.439999999999</v>
-      </c>
-      <c r="AG250" s="25">
+        <v>2935.23</v>
+      </c>
+      <c r="BD250" s="25">
         <f t="shared" si="156"/>
-        <v>831.17000000000007</v>
-      </c>
-      <c r="AH250" s="25">
+        <v>7264.18</v>
+      </c>
+      <c r="BE250" s="25">
         <f t="shared" si="156"/>
-        <v>10126.870000000001</v>
-      </c>
-      <c r="AI250" s="25">
+        <v>32108.460000000003</v>
+      </c>
+      <c r="BF250" s="25">
         <f t="shared" si="156"/>
-        <v>32661.549999999996</v>
-      </c>
-      <c r="AJ250" s="25">
-        <f t="shared" si="156"/>
-        <v>3765.18</v>
-      </c>
-      <c r="AK250" s="25">
-        <f t="shared" si="156"/>
-        <v>17726.560000000001</v>
-      </c>
-      <c r="AL250" s="25">
-        <f t="shared" si="156"/>
-        <v>15857.730000000005</v>
-      </c>
-      <c r="AM250" s="25">
-        <f t="shared" si="156"/>
-        <v>75696.620000000039</v>
-      </c>
-      <c r="AN250" s="25">
-        <f t="shared" si="156"/>
-        <v>0</v>
-      </c>
-      <c r="AO250" s="25">
-        <f t="shared" si="156"/>
-        <v>6941.9000000000005</v>
-      </c>
-      <c r="AP250" s="25">
-        <f t="shared" si="156"/>
-        <v>2654.6800000000003</v>
-      </c>
-      <c r="AQ250" s="25">
-        <f t="shared" si="156"/>
-        <v>0</v>
-      </c>
-      <c r="AR250" s="25">
-        <f t="shared" si="156"/>
-        <v>444.72</v>
-      </c>
-      <c r="AS250" s="25">
-        <f t="shared" si="156"/>
-        <v>6004.869999999999</v>
-      </c>
-      <c r="AT250" s="25">
-        <f t="shared" si="156"/>
-        <v>1489.28</v>
-      </c>
-      <c r="AU250" s="25">
-        <f t="shared" si="156"/>
-        <v>7206.3</v>
-      </c>
-      <c r="AV250" s="25">
-        <f t="shared" si="156"/>
-        <v>23458.619999999995</v>
-      </c>
-      <c r="AW250" s="25">
-        <f t="shared" si="156"/>
-        <v>5172.24</v>
-      </c>
-      <c r="AX250" s="25">
-        <f t="shared" si="156"/>
-        <v>9219.2400000000016</v>
-      </c>
-      <c r="AY250" s="25">
-        <f t="shared" si="156"/>
-        <v>7231.57</v>
-      </c>
-      <c r="AZ250" s="25">
-        <f t="shared" si="156"/>
-        <v>6886.05</v>
-      </c>
-      <c r="BA250" s="25">
-        <f t="shared" si="156"/>
-        <v>2079.8200000000002</v>
-      </c>
-      <c r="BB250" s="25">
-        <f t="shared" ref="BB250:BF250" si="157">SUM(BB5:BB249)</f>
-        <v>5804.1</v>
-      </c>
-      <c r="BC250" s="25">
-        <f t="shared" si="157"/>
-        <v>2935.23</v>
-      </c>
-      <c r="BD250" s="25">
-        <f t="shared" si="157"/>
-        <v>7264.18</v>
-      </c>
-      <c r="BE250" s="25">
-        <f t="shared" si="157"/>
-        <v>32108.460000000003</v>
-      </c>
-      <c r="BF250" s="25">
-        <f t="shared" si="157"/>
         <v>43588.159999999989</v>
       </c>
     </row>
-    <row r="251" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:58" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A251" s="25" t="s">
         <v>31</v>
       </c>
@@ -43660,6 +43660,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="L1:AA1"/>
     <mergeCell ref="AD2:AD4"/>
@@ -43676,22 +43692,6 @@
     <mergeCell ref="Y3:Y4"/>
     <mergeCell ref="Z3:Z4"/>
     <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <conditionalFormatting sqref="AC5:AD249">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -43712,35 +43712,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A5B878-3B18-453F-B9FC-7ADF8F2BA635}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100493764C60684DF4CB311E8C6DB824A31" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="81926f47a187cc63a92412ba9893c017">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6ddf8778-9569-40ed-9bf8-0f223cbd7521" xmlns:ns3="46728323-6609-471b-b746-bd6c0af0902a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6c744e4b291dae32e38cda089848b113" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100493764C60684DF4CB311E8C6DB824A31" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="622a8137851caf67f943ae43813a7cb3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6ddf8778-9569-40ed-9bf8-0f223cbd7521" xmlns:ns3="46728323-6609-471b-b746-bd6c0af0902a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74d04fb182727bc947f0574ca0cadd6" ns2:_="" ns3:_="">
     <xsd:import namespace="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
     <xsd:import namespace="46728323-6609-471b-b746-bd6c0af0902a"/>
     <xsd:element name="properties">
@@ -43790,7 +43770,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0d40e457-b01f-4f77-b199-af835d4d12ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0d40e457-b01f-4f77-b199-af835d4d12ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -43849,8 +43829,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -43939,40 +43919,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6ddf8778-9569-40ed-9bf8-0f223cbd7521">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="46728323-6609-471b-b746-bd6c0af0902a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2504252-4B69-4F73-B672-32B7F91F974C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
-    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCC898E8-4FC5-4A83-B96B-9F1DBDBE6043}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA7A8F-701B-4BD3-8EBF-76CA05E61F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6ddf8778-9569-40ed-9bf8-0f223cbd7521"/>
-    <ds:schemaRef ds:uri="46728323-6609-471b-b746-bd6c0af0902a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB6295A-3589-48F1-948F-179E4C7C3BF9}"/>
 </file>